--- a/week04-hands-on/data/법인매출통합.xlsx
+++ b/week04-hands-on/data/법인매출통합.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합데이터" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="법인별합계" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별피벗" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1003,4 +1004,140 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>법인명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>98000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>101000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>304000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>125000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>132000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>베트남</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3250000000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3480000000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3120000000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9850000000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15800000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16200000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14900000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>46900000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>890000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>920000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>875000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2685000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/week04-hands-on/data/법인매출통합.xlsx
+++ b/week04-hands-on/data/법인매출통합.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +27,27 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +55,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,513 +441,533 @@
   </sheetPr>
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>법인코드</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>법인명</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>통화</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CN01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>중국</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>890000</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>춘절 영향</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CN01</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>중국</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>920000</v>
       </c>
+      <c r="G3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CN01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>중국</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>875000</v>
       </c>
+      <c r="G4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>독일</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>98000</v>
       </c>
+      <c r="G5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>독일</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>105000</v>
       </c>
+      <c r="G6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>독일</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>101000</v>
       </c>
+      <c r="G7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>JP01</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>15800000</v>
       </c>
+      <c r="G8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>JP01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>16200000</v>
       </c>
+      <c r="G9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>JP01</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>14900000</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>시즌 영향</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>US01</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>125000</v>
       </c>
+      <c r="G11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>US01</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="3" t="n">
         <v>132000</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>신규 거래처 추가</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>US01</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="3" t="n">
         <v>118000</v>
       </c>
+      <c r="G13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>VN01</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>베트남</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="3" t="n">
         <v>3250000000</v>
       </c>
+      <c r="G14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>VN01</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>베트남</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="3" t="n">
         <v>3480000000</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>대형 프로젝트</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>VN01</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>베트남</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3" t="n">
         <v>3120000000</v>
       </c>
+      <c r="G16" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -938,66 +982,70 @@
   </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>법인명</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>매출합계</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>독일</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>304000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>375000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>베트남</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>9850000000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>46900000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>중국</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>2685000</v>
       </c>
     </row>
@@ -1014,126 +1062,133 @@
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>법인명</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>독일</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>98000</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>105000</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>101000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>304000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>125000</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>132000</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>118000</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>375000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>베트남</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>3250000000</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>3480000000</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3120000000</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>9850000000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>15800000</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>16200000</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>14900000</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>46900000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>중국</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>890000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>920000</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>875000</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>2685000</v>
       </c>
     </row>
